--- a/results/main/Figure_2_data_meta_0p25_heterogeneity_0_pet_peese.xlsx
+++ b/results/main/Figure_2_data_meta_0p25_heterogeneity_0_pet_peese.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="748">
   <si>
     <t xml:space="preserve">cID</t>
   </si>
@@ -1818,6 +1818,9 @@
   </si>
   <si>
     <t xml:space="preserve">439-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">439-3</t>
   </si>
   <si>
     <t xml:space="preserve">439-4</t>
@@ -25671,14 +25674,12 @@
       <c r="B564" t="n">
         <v>439</v>
       </c>
-      <c r="C564" t="n">
-        <v>0.0522992174761769</v>
-      </c>
-      <c r="D564" t="n">
-        <v>0</v>
+      <c r="C564"/>
+      <c r="D564" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E564" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F564" t="s">
         <v>104</v>
@@ -25695,14 +25696,10 @@
       <c r="J564" t="s">
         <v>22</v>
       </c>
-      <c r="K564" t="s">
-        <v>15</v>
-      </c>
-      <c r="L564" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="M564" t="n">
-        <v>0</v>
+      <c r="K564"/>
+      <c r="L564"/>
+      <c r="M564" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="565">
@@ -25710,19 +25707,19 @@
         <v>603</v>
       </c>
       <c r="B565" t="n">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="C565" t="n">
-        <v>0.052286533183728</v>
+        <v>0.0522992174761769</v>
       </c>
       <c r="D565" t="n">
         <v>0</v>
       </c>
       <c r="E565" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F565" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="G565" t="s">
         <v>20</v>
@@ -25754,13 +25751,13 @@
         <v>460</v>
       </c>
       <c r="C566" t="n">
-        <v>0.0501107224717052</v>
+        <v>0.052286533183728</v>
       </c>
       <c r="D566" t="n">
         <v>0</v>
       </c>
       <c r="E566" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F566" t="s">
         <v>127</v>
@@ -25781,7 +25778,7 @@
         <v>15</v>
       </c>
       <c r="L566" t="n">
-        <v>5.01</v>
+        <v>5.23</v>
       </c>
       <c r="M566" t="n">
         <v>0</v>
@@ -25795,13 +25792,13 @@
         <v>460</v>
       </c>
       <c r="C567" t="n">
-        <v>0.0500003345240809</v>
+        <v>0.0501107224717052</v>
       </c>
       <c r="D567" t="n">
         <v>0</v>
       </c>
       <c r="E567" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F567" t="s">
         <v>127</v>
@@ -25822,7 +25819,7 @@
         <v>15</v>
       </c>
       <c r="L567" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="M567" t="n">
         <v>0</v>
@@ -25836,16 +25833,16 @@
         <v>460</v>
       </c>
       <c r="C568" t="n">
-        <v>0.0500529886784011</v>
+        <v>0.0500003345240809</v>
       </c>
       <c r="D568" t="n">
         <v>0</v>
       </c>
       <c r="E568" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F568" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="G568" t="s">
         <v>20</v>
@@ -25863,7 +25860,7 @@
         <v>15</v>
       </c>
       <c r="L568" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="M568" t="n">
         <v>0</v>
@@ -25877,13 +25874,13 @@
         <v>460</v>
       </c>
       <c r="C569" t="n">
-        <v>0.057356638213643</v>
+        <v>0.0500529886784011</v>
       </c>
       <c r="D569" t="n">
         <v>0</v>
       </c>
       <c r="E569" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F569" t="s">
         <v>104</v>
@@ -25904,7 +25901,7 @@
         <v>15</v>
       </c>
       <c r="L569" t="n">
-        <v>5.74</v>
+        <v>5.01</v>
       </c>
       <c r="M569" t="n">
         <v>0</v>
@@ -25918,13 +25915,13 @@
         <v>460</v>
       </c>
       <c r="C570" t="n">
-        <v>0.0865149432542565</v>
+        <v>0.057356638213643</v>
       </c>
       <c r="D570" t="n">
         <v>0</v>
       </c>
       <c r="E570" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F570" t="s">
         <v>104</v>
@@ -25945,7 +25942,7 @@
         <v>15</v>
       </c>
       <c r="L570" t="n">
-        <v>8.65</v>
+        <v>5.74</v>
       </c>
       <c r="M570" t="n">
         <v>0</v>
@@ -25956,19 +25953,19 @@
         <v>609</v>
       </c>
       <c r="B571" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C571" t="n">
-        <v>0.0611647862127969</v>
+        <v>0.0865149432542565</v>
       </c>
       <c r="D571" t="n">
         <v>0</v>
       </c>
       <c r="E571" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F571" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="G571" t="s">
         <v>20</v>
@@ -25977,16 +25974,16 @@
         <v>15</v>
       </c>
       <c r="I571" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J571" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K571" t="s">
         <v>15</v>
       </c>
       <c r="L571" t="n">
-        <v>6.12</v>
+        <v>8.65</v>
       </c>
       <c r="M571" t="n">
         <v>0</v>
@@ -25997,19 +25994,19 @@
         <v>610</v>
       </c>
       <c r="B572" t="n">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="C572" t="n">
-        <v>0.0505541437718425</v>
+        <v>0.0611647862127969</v>
       </c>
       <c r="D572" t="n">
         <v>0</v>
       </c>
       <c r="E572" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F572" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G572" t="s">
         <v>20</v>
@@ -26018,16 +26015,16 @@
         <v>15</v>
       </c>
       <c r="I572" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J572" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K572" t="s">
         <v>15</v>
       </c>
       <c r="L572" t="n">
-        <v>5.06</v>
+        <v>6.12</v>
       </c>
       <c r="M572" t="n">
         <v>0</v>
@@ -26038,19 +26035,19 @@
         <v>611</v>
       </c>
       <c r="B573" t="n">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C573" t="n">
-        <v>0.053128410301962</v>
+        <v>0.0505541437718425</v>
       </c>
       <c r="D573" t="n">
         <v>0</v>
       </c>
       <c r="E573" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F573" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G573" t="s">
         <v>20</v>
@@ -26068,7 +26065,7 @@
         <v>15</v>
       </c>
       <c r="L573" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
       <c r="M573" t="n">
         <v>0</v>
@@ -26082,7 +26079,7 @@
         <v>496</v>
       </c>
       <c r="C574" t="n">
-        <v>0.0513900839646608</v>
+        <v>0.053128410301962</v>
       </c>
       <c r="D574" t="n">
         <v>0</v>
@@ -26109,7 +26106,7 @@
         <v>15</v>
       </c>
       <c r="L574" t="n">
-        <v>5.14</v>
+        <v>5.31</v>
       </c>
       <c r="M574" t="n">
         <v>0</v>
@@ -26120,19 +26117,19 @@
         <v>613</v>
       </c>
       <c r="B575" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C575" t="n">
-        <v>0.0688440914114233</v>
+        <v>0.0513900839646608</v>
       </c>
       <c r="D575" t="n">
         <v>0</v>
       </c>
       <c r="E575" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F575" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G575" t="s">
         <v>20</v>
@@ -26150,7 +26147,7 @@
         <v>15</v>
       </c>
       <c r="L575" t="n">
-        <v>6.88</v>
+        <v>5.14</v>
       </c>
       <c r="M575" t="n">
         <v>0</v>
@@ -26164,7 +26161,7 @@
         <v>500</v>
       </c>
       <c r="C576" t="n">
-        <v>0.0950330233830725</v>
+        <v>0.0688440914114233</v>
       </c>
       <c r="D576" t="n">
         <v>0</v>
@@ -26191,7 +26188,7 @@
         <v>15</v>
       </c>
       <c r="L576" t="n">
-        <v>9.5</v>
+        <v>6.88</v>
       </c>
       <c r="M576" t="n">
         <v>0</v>
@@ -26205,13 +26202,13 @@
         <v>500</v>
       </c>
       <c r="C577" t="n">
-        <v>0.0562935203297237</v>
+        <v>0.0950330233830725</v>
       </c>
       <c r="D577" t="n">
         <v>0</v>
       </c>
       <c r="E577" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F577" t="s">
         <v>104</v>
@@ -26232,7 +26229,7 @@
         <v>15</v>
       </c>
       <c r="L577" t="n">
-        <v>5.63</v>
+        <v>9.5</v>
       </c>
       <c r="M577" t="n">
         <v>0</v>
@@ -26246,7 +26243,7 @@
         <v>500</v>
       </c>
       <c r="C578" t="n">
-        <v>0.0865668725683253</v>
+        <v>0.0562935203297237</v>
       </c>
       <c r="D578" t="n">
         <v>0</v>
@@ -26273,7 +26270,7 @@
         <v>15</v>
       </c>
       <c r="L578" t="n">
-        <v>8.66</v>
+        <v>5.63</v>
       </c>
       <c r="M578" t="n">
         <v>0</v>
@@ -26287,13 +26284,13 @@
         <v>500</v>
       </c>
       <c r="C579" t="n">
-        <v>0.0670735385139558</v>
+        <v>0.0865668725683253</v>
       </c>
       <c r="D579" t="n">
         <v>0</v>
       </c>
       <c r="E579" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F579" t="s">
         <v>104</v>
@@ -26314,7 +26311,7 @@
         <v>15</v>
       </c>
       <c r="L579" t="n">
-        <v>6.71</v>
+        <v>8.66</v>
       </c>
       <c r="M579" t="n">
         <v>0</v>
@@ -26325,28 +26322,28 @@
         <v>618</v>
       </c>
       <c r="B580" t="n">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="C580" t="n">
-        <v>0.0506674586539439</v>
+        <v>0.0670735385139558</v>
       </c>
       <c r="D580" t="n">
         <v>0</v>
       </c>
       <c r="E580" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F580" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G580" t="s">
         <v>20</v>
       </c>
       <c r="H580" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I580" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J580" t="s">
         <v>22</v>
@@ -26355,7 +26352,7 @@
         <v>15</v>
       </c>
       <c r="L580" t="n">
-        <v>5.07</v>
+        <v>6.71</v>
       </c>
       <c r="M580" t="n">
         <v>0</v>
@@ -26369,13 +26366,13 @@
         <v>533</v>
       </c>
       <c r="C581" t="n">
-        <v>0.0528417045354207</v>
+        <v>0.0506674586539439</v>
       </c>
       <c r="D581" t="n">
         <v>0</v>
       </c>
       <c r="E581" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F581" t="s">
         <v>14</v>
@@ -26396,7 +26393,7 @@
         <v>15</v>
       </c>
       <c r="L581" t="n">
-        <v>5.28</v>
+        <v>5.07</v>
       </c>
       <c r="M581" t="n">
         <v>0</v>
@@ -26410,13 +26407,13 @@
         <v>533</v>
       </c>
       <c r="C582" t="n">
-        <v>0.0500016828752597</v>
+        <v>0.0528417045354207</v>
       </c>
       <c r="D582" t="n">
         <v>0</v>
       </c>
       <c r="E582" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F582" t="s">
         <v>14</v>
@@ -26437,7 +26434,7 @@
         <v>15</v>
       </c>
       <c r="L582" t="n">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="M582" t="n">
         <v>0</v>
@@ -26451,13 +26448,13 @@
         <v>533</v>
       </c>
       <c r="C583" t="n">
-        <v>0.0507449309578771</v>
+        <v>0.0500016828752597</v>
       </c>
       <c r="D583" t="n">
         <v>0</v>
       </c>
       <c r="E583" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F583" t="s">
         <v>14</v>
@@ -26478,7 +26475,7 @@
         <v>15</v>
       </c>
       <c r="L583" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="M583" t="n">
         <v>0</v>
@@ -26492,13 +26489,13 @@
         <v>533</v>
       </c>
       <c r="C584" t="n">
-        <v>0.0500181528438445</v>
+        <v>0.0507449309578771</v>
       </c>
       <c r="D584" t="n">
         <v>0</v>
       </c>
       <c r="E584" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F584" t="s">
         <v>14</v>
@@ -26519,7 +26516,7 @@
         <v>15</v>
       </c>
       <c r="L584" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="M584" t="n">
         <v>0</v>
@@ -26533,13 +26530,13 @@
         <v>533</v>
       </c>
       <c r="C585" t="n">
-        <v>0.0502082494507158</v>
+        <v>0.0500181528438445</v>
       </c>
       <c r="D585" t="n">
         <v>0</v>
       </c>
       <c r="E585" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F585" t="s">
         <v>14</v>
@@ -26560,7 +26557,7 @@
         <v>15</v>
       </c>
       <c r="L585" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
       <c r="M585" t="n">
         <v>0</v>
@@ -26574,13 +26571,13 @@
         <v>533</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0526168459658128</v>
+        <v>0.0502082494507158</v>
       </c>
       <c r="D586" t="n">
         <v>0</v>
       </c>
       <c r="E586" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F586" t="s">
         <v>14</v>
@@ -26601,7 +26598,7 @@
         <v>15</v>
       </c>
       <c r="L586" t="n">
-        <v>5.26</v>
+        <v>5.02</v>
       </c>
       <c r="M586" t="n">
         <v>0</v>
@@ -26615,13 +26612,13 @@
         <v>533</v>
       </c>
       <c r="C587" t="n">
-        <v>0.0519772368832326</v>
+        <v>0.0526168459658128</v>
       </c>
       <c r="D587" t="n">
         <v>0</v>
       </c>
       <c r="E587" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F587" t="s">
         <v>14</v>
@@ -26642,7 +26639,7 @@
         <v>15</v>
       </c>
       <c r="L587" t="n">
-        <v>5.2</v>
+        <v>5.26</v>
       </c>
       <c r="M587" t="n">
         <v>0</v>
@@ -26653,40 +26650,40 @@
         <v>626</v>
       </c>
       <c r="B588" t="n">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C588" t="n">
-        <v>0.0592989287447361</v>
+        <v>0.0519772368832326</v>
       </c>
       <c r="D588" t="n">
-        <v>0.00302571860816944</v>
+        <v>0</v>
       </c>
       <c r="E588" t="n">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="F588" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G588" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H588" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I588" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J588" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K588" t="s">
         <v>15</v>
       </c>
       <c r="L588" t="n">
-        <v>5.93</v>
+        <v>5.2</v>
       </c>
       <c r="M588" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="589">
@@ -26694,16 +26691,16 @@
         <v>627</v>
       </c>
       <c r="B589" t="n">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C589" t="n">
-        <v>0.0712772421884067</v>
+        <v>0.0592989287447361</v>
       </c>
       <c r="D589" t="n">
-        <v>0.00987654320987654</v>
+        <v>0.00302571860816944</v>
       </c>
       <c r="E589" t="n">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="F589" t="s">
         <v>26</v>
@@ -26715,7 +26712,7 @@
         <v>15</v>
       </c>
       <c r="I589" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J589" t="s">
         <v>17</v>
@@ -26724,10 +26721,10 @@
         <v>15</v>
       </c>
       <c r="L589" t="n">
-        <v>7.13</v>
+        <v>5.93</v>
       </c>
       <c r="M589" t="n">
-        <v>0.99</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="590">
@@ -26738,13 +26735,13 @@
         <v>547</v>
       </c>
       <c r="C590" t="n">
-        <v>0.0501531899925308</v>
+        <v>0.0712772421884067</v>
       </c>
       <c r="D590" t="n">
-        <v>0</v>
+        <v>0.00987654320987654</v>
       </c>
       <c r="E590" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F590" t="s">
         <v>26</v>
@@ -26765,10 +26762,10 @@
         <v>15</v>
       </c>
       <c r="L590" t="n">
-        <v>5.02</v>
+        <v>7.13</v>
       </c>
       <c r="M590" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="591">
@@ -26779,13 +26776,13 @@
         <v>547</v>
       </c>
       <c r="C591" t="n">
-        <v>0.12114374908814</v>
+        <v>0.0501531899925308</v>
       </c>
       <c r="D591" t="n">
-        <v>0.0404040404040404</v>
+        <v>0</v>
       </c>
       <c r="E591" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F591" t="s">
         <v>26</v>
@@ -26806,10 +26803,10 @@
         <v>15</v>
       </c>
       <c r="L591" t="n">
-        <v>12.11</v>
+        <v>5.02</v>
       </c>
       <c r="M591" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="592">
@@ -26820,13 +26817,13 @@
         <v>547</v>
       </c>
       <c r="C592" t="n">
-        <v>0.571876235186465</v>
+        <v>0.12114374908814</v>
       </c>
       <c r="D592" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.0404040404040404</v>
       </c>
       <c r="E592" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F592" t="s">
         <v>26</v>
@@ -26847,10 +26844,10 @@
         <v>15</v>
       </c>
       <c r="L592" t="n">
-        <v>57.19</v>
+        <v>12.11</v>
       </c>
       <c r="M592" t="n">
-        <v>4.26</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="593">
@@ -26861,13 +26858,13 @@
         <v>547</v>
       </c>
       <c r="C593" t="n">
-        <v>0.0503185767921326</v>
+        <v>0.571876235186465</v>
       </c>
       <c r="D593" t="n">
-        <v>0</v>
+        <v>0.0425531914893617</v>
       </c>
       <c r="E593" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F593" t="s">
         <v>26</v>
@@ -26888,10 +26885,10 @@
         <v>15</v>
       </c>
       <c r="L593" t="n">
-        <v>5.03</v>
+        <v>57.19</v>
       </c>
       <c r="M593" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="594">
@@ -26902,13 +26899,13 @@
         <v>547</v>
       </c>
       <c r="C594" t="n">
-        <v>0.0505313969925155</v>
+        <v>0.0503185767921326</v>
       </c>
       <c r="D594" t="n">
         <v>0</v>
       </c>
       <c r="E594" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F594" t="s">
         <v>26</v>
@@ -26929,7 +26926,7 @@
         <v>15</v>
       </c>
       <c r="L594" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="M594" t="n">
         <v>0</v>
@@ -26943,13 +26940,13 @@
         <v>547</v>
       </c>
       <c r="C595" t="n">
-        <v>0.0518846070339971</v>
+        <v>0.0505313969925155</v>
       </c>
       <c r="D595" t="n">
         <v>0</v>
       </c>
       <c r="E595" t="n">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="F595" t="s">
         <v>26</v>
@@ -26970,7 +26967,7 @@
         <v>15</v>
       </c>
       <c r="L595" t="n">
-        <v>5.19</v>
+        <v>5.05</v>
       </c>
       <c r="M595" t="n">
         <v>0</v>
@@ -26984,13 +26981,13 @@
         <v>547</v>
       </c>
       <c r="C596" t="n">
-        <v>0.0811494183098004</v>
+        <v>0.0518846070339971</v>
       </c>
       <c r="D596" t="n">
-        <v>0.0213903743315508</v>
+        <v>0</v>
       </c>
       <c r="E596" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F596" t="s">
         <v>26</v>
@@ -27011,10 +27008,10 @@
         <v>15</v>
       </c>
       <c r="L596" t="n">
-        <v>8.11</v>
+        <v>5.19</v>
       </c>
       <c r="M596" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="597">
@@ -27022,16 +27019,16 @@
         <v>635</v>
       </c>
       <c r="B597" t="n">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="C597" t="n">
-        <v>0.0803387371463793</v>
+        <v>0.0811494183098004</v>
       </c>
       <c r="D597" t="n">
-        <v>0.161290322580645</v>
+        <v>0.0213903743315508</v>
       </c>
       <c r="E597" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F597" t="s">
         <v>26</v>
@@ -27043,7 +27040,7 @@
         <v>15</v>
       </c>
       <c r="I597" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J597" t="s">
         <v>17</v>
@@ -27052,10 +27049,10 @@
         <v>15</v>
       </c>
       <c r="L597" t="n">
-        <v>8.03</v>
+        <v>8.11</v>
       </c>
       <c r="M597" t="n">
-        <v>16.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="598">
@@ -27066,13 +27063,13 @@
         <v>566</v>
       </c>
       <c r="C598" t="n">
-        <v>0.0514871332858951</v>
+        <v>0.0803387371463793</v>
       </c>
       <c r="D598" t="n">
-        <v>0</v>
+        <v>0.161290322580645</v>
       </c>
       <c r="E598" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F598" t="s">
         <v>26</v>
@@ -27093,10 +27090,10 @@
         <v>15</v>
       </c>
       <c r="L598" t="n">
-        <v>5.15</v>
+        <v>8.03</v>
       </c>
       <c r="M598" t="n">
-        <v>0</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="599">
@@ -27107,13 +27104,13 @@
         <v>566</v>
       </c>
       <c r="C599" t="n">
-        <v>0.0682971055790871</v>
+        <v>0.0514871332858951</v>
       </c>
       <c r="D599" t="n">
-        <v>0.0103092783505155</v>
+        <v>0</v>
       </c>
       <c r="E599" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F599" t="s">
         <v>26</v>
@@ -27134,10 +27131,10 @@
         <v>15</v>
       </c>
       <c r="L599" t="n">
-        <v>6.83</v>
+        <v>5.15</v>
       </c>
       <c r="M599" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="600">
@@ -27148,13 +27145,13 @@
         <v>566</v>
       </c>
       <c r="C600" t="n">
-        <v>0.648782024715854</v>
+        <v>0.0682971055790871</v>
       </c>
       <c r="D600" t="n">
-        <v>0.455223880597015</v>
+        <v>0.0103092783505155</v>
       </c>
       <c r="E600" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F600" t="s">
         <v>26</v>
@@ -27175,10 +27172,10 @@
         <v>15</v>
       </c>
       <c r="L600" t="n">
-        <v>64.88</v>
+        <v>6.83</v>
       </c>
       <c r="M600" t="n">
-        <v>45.52</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="601">
@@ -27189,13 +27186,13 @@
         <v>566</v>
       </c>
       <c r="C601" t="n">
-        <v>0.0902350563255633</v>
+        <v>0.648782024715854</v>
       </c>
       <c r="D601" t="n">
-        <v>0.135714285714286</v>
+        <v>0.455223880597015</v>
       </c>
       <c r="E601" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F601" t="s">
         <v>26</v>
@@ -27216,10 +27213,10 @@
         <v>15</v>
       </c>
       <c r="L601" t="n">
-        <v>9.02</v>
+        <v>64.88</v>
       </c>
       <c r="M601" t="n">
-        <v>13.57</v>
+        <v>45.52</v>
       </c>
     </row>
     <row r="602">
@@ -27230,13 +27227,13 @@
         <v>566</v>
       </c>
       <c r="C602" t="n">
-        <v>0.0861977499031187</v>
+        <v>0.0902350563255633</v>
       </c>
       <c r="D602" t="n">
-        <v>0.0632911392405063</v>
+        <v>0.135714285714286</v>
       </c>
       <c r="E602" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F602" t="s">
         <v>26</v>
@@ -27257,10 +27254,10 @@
         <v>15</v>
       </c>
       <c r="L602" t="n">
-        <v>8.62</v>
+        <v>9.02</v>
       </c>
       <c r="M602" t="n">
-        <v>6.33</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="603">
@@ -27271,13 +27268,13 @@
         <v>566</v>
       </c>
       <c r="C603" t="n">
-        <v>0.0503474308114704</v>
+        <v>0.0861977499031187</v>
       </c>
       <c r="D603" t="n">
-        <v>0</v>
+        <v>0.0632911392405063</v>
       </c>
       <c r="E603" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F603" t="s">
         <v>26</v>
@@ -27298,10 +27295,10 @@
         <v>15</v>
       </c>
       <c r="L603" t="n">
-        <v>5.03</v>
+        <v>8.62</v>
       </c>
       <c r="M603" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="604">
@@ -27312,13 +27309,13 @@
         <v>566</v>
       </c>
       <c r="C604" t="n">
-        <v>0.053097626285369</v>
+        <v>0.0503474308114704</v>
       </c>
       <c r="D604" t="n">
         <v>0</v>
       </c>
       <c r="E604" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F604" t="s">
         <v>26</v>
@@ -27339,7 +27336,7 @@
         <v>15</v>
       </c>
       <c r="L604" t="n">
-        <v>5.31</v>
+        <v>5.03</v>
       </c>
       <c r="M604" t="n">
         <v>0</v>
@@ -27353,13 +27350,13 @@
         <v>566</v>
       </c>
       <c r="C605" t="n">
-        <v>0.114560234635306</v>
+        <v>0.053097626285369</v>
       </c>
       <c r="D605" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E605" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F605" t="s">
         <v>26</v>
@@ -27380,10 +27377,10 @@
         <v>15</v>
       </c>
       <c r="L605" t="n">
-        <v>11.46</v>
+        <v>5.31</v>
       </c>
       <c r="M605" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="606">
@@ -27394,13 +27391,13 @@
         <v>566</v>
       </c>
       <c r="C606" t="n">
-        <v>0.0632671370409362</v>
+        <v>0.114560234635306</v>
       </c>
       <c r="D606" t="n">
-        <v>0.0540540540540541</v>
+        <v>0.125</v>
       </c>
       <c r="E606" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F606" t="s">
         <v>26</v>
@@ -27421,10 +27418,10 @@
         <v>15</v>
       </c>
       <c r="L606" t="n">
-        <v>6.33</v>
+        <v>11.46</v>
       </c>
       <c r="M606" t="n">
-        <v>5.41</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="607">
@@ -27435,13 +27432,13 @@
         <v>566</v>
       </c>
       <c r="C607" t="n">
-        <v>0.0622189507659768</v>
+        <v>0.0632671370409362</v>
       </c>
       <c r="D607" t="n">
-        <v>0</v>
+        <v>0.0540540540540541</v>
       </c>
       <c r="E607" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F607" t="s">
         <v>26</v>
@@ -27462,10 +27459,10 @@
         <v>15</v>
       </c>
       <c r="L607" t="n">
-        <v>6.22</v>
+        <v>6.33</v>
       </c>
       <c r="M607" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="608">
@@ -27473,37 +27470,37 @@
         <v>646</v>
       </c>
       <c r="B608" t="n">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="C608" t="n">
-        <v>0.0624822999979501</v>
+        <v>0.0622189507659768</v>
       </c>
       <c r="D608" t="n">
         <v>0</v>
       </c>
       <c r="E608" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F608" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G608" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H608" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I608" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J608" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K608" t="s">
         <v>15</v>
       </c>
       <c r="L608" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="M608" t="n">
         <v>0</v>
@@ -27517,13 +27514,13 @@
         <v>581</v>
       </c>
       <c r="C609" t="n">
-        <v>0.0609656697719876</v>
+        <v>0.0624822999979501</v>
       </c>
       <c r="D609" t="n">
         <v>0</v>
       </c>
       <c r="E609" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F609" t="s">
         <v>24</v>
@@ -27544,7 +27541,7 @@
         <v>15</v>
       </c>
       <c r="L609" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="M609" t="n">
         <v>0</v>
@@ -27555,28 +27552,28 @@
         <v>648</v>
       </c>
       <c r="B610" t="n">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="C610" t="n">
-        <v>0.32146198092626</v>
+        <v>0.0609656697719876</v>
       </c>
       <c r="D610" t="n">
-        <v>0.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="E610" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F610" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G610" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H610" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I610" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J610" t="s">
         <v>22</v>
@@ -27585,10 +27582,10 @@
         <v>15</v>
       </c>
       <c r="L610" t="n">
-        <v>32.15</v>
+        <v>6.1</v>
       </c>
       <c r="M610" t="n">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="611">
@@ -27599,13 +27596,13 @@
         <v>608</v>
       </c>
       <c r="C611" t="n">
-        <v>0.239310906982224</v>
+        <v>0.32146198092626</v>
       </c>
       <c r="D611" t="n">
-        <v>0.176470588235294</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="E611" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F611" t="s">
         <v>19</v>
@@ -27626,10 +27623,10 @@
         <v>15</v>
       </c>
       <c r="L611" t="n">
-        <v>23.93</v>
+        <v>32.15</v>
       </c>
       <c r="M611" t="n">
-        <v>17.65</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="612">
@@ -27640,13 +27637,13 @@
         <v>608</v>
       </c>
       <c r="C612" t="n">
-        <v>0.999999999999963</v>
+        <v>0.239310906982224</v>
       </c>
       <c r="D612" t="n">
-        <v>0.545454545454545</v>
+        <v>0.176470588235294</v>
       </c>
       <c r="E612" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F612" t="s">
         <v>19</v>
@@ -27664,13 +27661,13 @@
         <v>22</v>
       </c>
       <c r="K612" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L612" t="n">
-        <v>100</v>
+        <v>23.93</v>
       </c>
       <c r="M612" t="n">
-        <v>54.55</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="613">
@@ -27678,19 +27675,19 @@
         <v>651</v>
       </c>
       <c r="B613" t="n">
-        <v>62</v>
+        <v>608</v>
       </c>
       <c r="C613" t="n">
-        <v>0.0542792963449549</v>
+        <v>0.999999999999963</v>
       </c>
       <c r="D613" t="n">
-        <v>0</v>
+        <v>0.545454545454545</v>
       </c>
       <c r="E613" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F613" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G613" t="s">
         <v>15</v>
@@ -27699,19 +27696,19 @@
         <v>15</v>
       </c>
       <c r="I613" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J613" t="s">
         <v>22</v>
       </c>
       <c r="K613" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L613" t="n">
-        <v>5.43</v>
+        <v>100</v>
       </c>
       <c r="M613" t="n">
-        <v>0</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="614">
@@ -27722,13 +27719,13 @@
         <v>62</v>
       </c>
       <c r="C614" t="n">
-        <v>0.0623100167940237</v>
+        <v>0.0542792963449549</v>
       </c>
       <c r="D614" t="n">
         <v>0</v>
       </c>
       <c r="E614" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F614" t="s">
         <v>14</v>
@@ -27749,7 +27746,7 @@
         <v>15</v>
       </c>
       <c r="L614" t="n">
-        <v>6.23</v>
+        <v>5.43</v>
       </c>
       <c r="M614" t="n">
         <v>0</v>
@@ -27760,19 +27757,19 @@
         <v>653</v>
       </c>
       <c r="B615" t="n">
-        <v>623</v>
+        <v>62</v>
       </c>
       <c r="C615" t="n">
-        <v>0.0520375050410668</v>
+        <v>0.0623100167940237</v>
       </c>
       <c r="D615" t="n">
         <v>0</v>
       </c>
       <c r="E615" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F615" t="s">
-        <v>393</v>
+        <v>14</v>
       </c>
       <c r="G615" t="s">
         <v>15</v>
@@ -27781,7 +27778,7 @@
         <v>15</v>
       </c>
       <c r="I615" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J615" t="s">
         <v>22</v>
@@ -27790,7 +27787,7 @@
         <v>15</v>
       </c>
       <c r="L615" t="n">
-        <v>5.2</v>
+        <v>6.23</v>
       </c>
       <c r="M615" t="n">
         <v>0</v>
@@ -27804,13 +27801,13 @@
         <v>623</v>
       </c>
       <c r="C616" t="n">
-        <v>0.138586465743367</v>
+        <v>0.0520375050410668</v>
       </c>
       <c r="D616" t="n">
-        <v>0.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="E616" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F616" t="s">
         <v>393</v>
@@ -27831,10 +27828,10 @@
         <v>15</v>
       </c>
       <c r="L616" t="n">
-        <v>13.86</v>
+        <v>5.2</v>
       </c>
       <c r="M616" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="617">
@@ -27842,19 +27839,19 @@
         <v>655</v>
       </c>
       <c r="B617" t="n">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C617" t="n">
-        <v>0.0689275562678226</v>
+        <v>0.138586465743367</v>
       </c>
       <c r="D617" t="n">
-        <v>0.0661157024793388</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E617" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F617" t="s">
-        <v>26</v>
+        <v>393</v>
       </c>
       <c r="G617" t="s">
         <v>15</v>
@@ -27866,16 +27863,16 @@
         <v>34</v>
       </c>
       <c r="J617" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K617" t="s">
         <v>15</v>
       </c>
       <c r="L617" t="n">
-        <v>6.89</v>
+        <v>13.86</v>
       </c>
       <c r="M617" t="n">
-        <v>6.61</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="618">
@@ -27886,13 +27883,13 @@
         <v>624</v>
       </c>
       <c r="C618" t="n">
-        <v>0.0503119420824597</v>
+        <v>0.0689275562678226</v>
       </c>
       <c r="D618" t="n">
-        <v>0</v>
+        <v>0.0661157024793388</v>
       </c>
       <c r="E618" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="F618" t="s">
         <v>26</v>
@@ -27913,10 +27910,10 @@
         <v>15</v>
       </c>
       <c r="L618" t="n">
-        <v>5.03</v>
+        <v>6.89</v>
       </c>
       <c r="M618" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="619">
@@ -27927,13 +27924,13 @@
         <v>624</v>
       </c>
       <c r="C619" t="n">
-        <v>0.0585934369282221</v>
+        <v>0.0503119420824597</v>
       </c>
       <c r="D619" t="n">
-        <v>0.00555555555555556</v>
+        <v>0</v>
       </c>
       <c r="E619" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F619" t="s">
         <v>26</v>
@@ -27954,10 +27951,10 @@
         <v>15</v>
       </c>
       <c r="L619" t="n">
-        <v>5.86</v>
+        <v>5.03</v>
       </c>
       <c r="M619" t="n">
-        <v>0.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="620">
@@ -27965,40 +27962,40 @@
         <v>658</v>
       </c>
       <c r="B620" t="n">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C620" t="n">
-        <v>0.0503658156511116</v>
+        <v>0.0585934369282221</v>
       </c>
       <c r="D620" t="n">
-        <v>0</v>
+        <v>0.00555555555555556</v>
       </c>
       <c r="E620" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="F620" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="G620" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H620" t="s">
         <v>15</v>
       </c>
       <c r="I620" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J620" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K620" t="s">
         <v>15</v>
       </c>
       <c r="L620" t="n">
-        <v>5.04</v>
+        <v>5.86</v>
       </c>
       <c r="M620" t="n">
-        <v>0</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="621">
@@ -28009,13 +28006,13 @@
         <v>625</v>
       </c>
       <c r="C621" t="n">
-        <v>0.0704723841542362</v>
+        <v>0.0503658156511116</v>
       </c>
       <c r="D621" t="n">
-        <v>0.0273972602739726</v>
+        <v>0</v>
       </c>
       <c r="E621" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F621" t="s">
         <v>100</v>
@@ -28036,10 +28033,10 @@
         <v>15</v>
       </c>
       <c r="L621" t="n">
-        <v>7.05</v>
+        <v>5.04</v>
       </c>
       <c r="M621" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
@@ -28050,13 +28047,13 @@
         <v>625</v>
       </c>
       <c r="C622" t="n">
-        <v>0.0541481413276136</v>
+        <v>0.0704723841542362</v>
       </c>
       <c r="D622" t="n">
-        <v>0</v>
+        <v>0.0273972602739726</v>
       </c>
       <c r="E622" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F622" t="s">
         <v>100</v>
@@ -28077,10 +28074,10 @@
         <v>15</v>
       </c>
       <c r="L622" t="n">
-        <v>5.41</v>
+        <v>7.05</v>
       </c>
       <c r="M622" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="623">
@@ -28088,19 +28085,19 @@
         <v>661</v>
       </c>
       <c r="B623" t="n">
-        <v>63</v>
+        <v>625</v>
       </c>
       <c r="C623" t="n">
-        <v>0.0559715291401123</v>
+        <v>0.0541481413276136</v>
       </c>
       <c r="D623" t="n">
         <v>0</v>
       </c>
       <c r="E623" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F623" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G623" t="s">
         <v>20</v>
@@ -28118,7 +28115,7 @@
         <v>15</v>
       </c>
       <c r="L623" t="n">
-        <v>5.6</v>
+        <v>5.41</v>
       </c>
       <c r="M623" t="n">
         <v>0</v>
@@ -28132,13 +28129,13 @@
         <v>63</v>
       </c>
       <c r="C624" t="n">
-        <v>0.0509658218731418</v>
+        <v>0.0559715291401123</v>
       </c>
       <c r="D624" t="n">
         <v>0</v>
       </c>
       <c r="E624" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F624" t="s">
         <v>104</v>
@@ -28159,7 +28156,7 @@
         <v>15</v>
       </c>
       <c r="L624" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="M624" t="n">
         <v>0</v>
@@ -28173,7 +28170,7 @@
         <v>63</v>
       </c>
       <c r="C625" t="n">
-        <v>0.0552769681615504</v>
+        <v>0.0509658218731418</v>
       </c>
       <c r="D625" t="n">
         <v>0</v>
@@ -28200,7 +28197,7 @@
         <v>15</v>
       </c>
       <c r="L625" t="n">
-        <v>5.53</v>
+        <v>5.1</v>
       </c>
       <c r="M625" t="n">
         <v>0</v>
@@ -28214,13 +28211,13 @@
         <v>63</v>
       </c>
       <c r="C626" t="n">
-        <v>0.0553516232052586</v>
+        <v>0.0552769681615504</v>
       </c>
       <c r="D626" t="n">
         <v>0</v>
       </c>
       <c r="E626" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F626" t="s">
         <v>104</v>
@@ -28241,7 +28238,7 @@
         <v>15</v>
       </c>
       <c r="L626" t="n">
-        <v>5.54</v>
+        <v>5.53</v>
       </c>
       <c r="M626" t="n">
         <v>0</v>
@@ -28255,13 +28252,13 @@
         <v>63</v>
       </c>
       <c r="C627" t="n">
-        <v>0.0539817544081159</v>
+        <v>0.0553516232052586</v>
       </c>
       <c r="D627" t="n">
         <v>0</v>
       </c>
       <c r="E627" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>104</v>
@@ -28282,7 +28279,7 @@
         <v>15</v>
       </c>
       <c r="L627" t="n">
-        <v>5.4</v>
+        <v>5.54</v>
       </c>
       <c r="M627" t="n">
         <v>0</v>
@@ -28296,13 +28293,13 @@
         <v>63</v>
       </c>
       <c r="C628" t="n">
-        <v>0.0508969395448472</v>
+        <v>0.0539817544081159</v>
       </c>
       <c r="D628" t="n">
         <v>0</v>
       </c>
       <c r="E628" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F628" t="s">
         <v>104</v>
@@ -28323,7 +28320,7 @@
         <v>15</v>
       </c>
       <c r="L628" t="n">
-        <v>5.09</v>
+        <v>5.4</v>
       </c>
       <c r="M628" t="n">
         <v>0</v>
@@ -28337,13 +28334,13 @@
         <v>63</v>
       </c>
       <c r="C629" t="n">
-        <v>0.0535257628255615</v>
+        <v>0.0508969395448472</v>
       </c>
       <c r="D629" t="n">
         <v>0</v>
       </c>
       <c r="E629" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F629" t="s">
         <v>104</v>
@@ -28364,7 +28361,7 @@
         <v>15</v>
       </c>
       <c r="L629" t="n">
-        <v>5.35</v>
+        <v>5.09</v>
       </c>
       <c r="M629" t="n">
         <v>0</v>
@@ -28378,13 +28375,13 @@
         <v>63</v>
       </c>
       <c r="C630" t="n">
-        <v>0.0501766159918525</v>
+        <v>0.0535257628255615</v>
       </c>
       <c r="D630" t="n">
         <v>0</v>
       </c>
       <c r="E630" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F630" t="s">
         <v>104</v>
@@ -28405,7 +28402,7 @@
         <v>15</v>
       </c>
       <c r="L630" t="n">
-        <v>5.02</v>
+        <v>5.35</v>
       </c>
       <c r="M630" t="n">
         <v>0</v>
@@ -28419,13 +28416,13 @@
         <v>63</v>
       </c>
       <c r="C631" t="n">
-        <v>0.0542968860382236</v>
+        <v>0.0501766159918525</v>
       </c>
       <c r="D631" t="n">
         <v>0</v>
       </c>
       <c r="E631" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F631" t="s">
         <v>104</v>
@@ -28446,7 +28443,7 @@
         <v>15</v>
       </c>
       <c r="L631" t="n">
-        <v>5.43</v>
+        <v>5.02</v>
       </c>
       <c r="M631" t="n">
         <v>0</v>
@@ -28460,13 +28457,13 @@
         <v>63</v>
       </c>
       <c r="C632" t="n">
-        <v>0.0563764012847899</v>
+        <v>0.0542968860382236</v>
       </c>
       <c r="D632" t="n">
         <v>0</v>
       </c>
       <c r="E632" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F632" t="s">
         <v>104</v>
@@ -28487,7 +28484,7 @@
         <v>15</v>
       </c>
       <c r="L632" t="n">
-        <v>5.64</v>
+        <v>5.43</v>
       </c>
       <c r="M632" t="n">
         <v>0</v>
@@ -28501,13 +28498,13 @@
         <v>63</v>
       </c>
       <c r="C633" t="n">
-        <v>0.0528502126580379</v>
+        <v>0.0563764012847899</v>
       </c>
       <c r="D633" t="n">
         <v>0</v>
       </c>
       <c r="E633" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>104</v>
@@ -28528,7 +28525,7 @@
         <v>15</v>
       </c>
       <c r="L633" t="n">
-        <v>5.29</v>
+        <v>5.64</v>
       </c>
       <c r="M633" t="n">
         <v>0</v>
@@ -28542,13 +28539,13 @@
         <v>63</v>
       </c>
       <c r="C634" t="n">
-        <v>0.0569773380028176</v>
+        <v>0.0528502126580379</v>
       </c>
       <c r="D634" t="n">
         <v>0</v>
       </c>
       <c r="E634" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F634" t="s">
         <v>104</v>
@@ -28569,7 +28566,7 @@
         <v>15</v>
       </c>
       <c r="L634" t="n">
-        <v>5.7</v>
+        <v>5.29</v>
       </c>
       <c r="M634" t="n">
         <v>0</v>
@@ -28583,13 +28580,13 @@
         <v>63</v>
       </c>
       <c r="C635" t="n">
-        <v>0.0500002702853112</v>
+        <v>0.0569773380028176</v>
       </c>
       <c r="D635" t="n">
         <v>0</v>
       </c>
       <c r="E635" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F635" t="s">
         <v>104</v>
@@ -28610,7 +28607,7 @@
         <v>15</v>
       </c>
       <c r="L635" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="M635" t="n">
         <v>0</v>
@@ -28624,13 +28621,13 @@
         <v>63</v>
       </c>
       <c r="C636" t="n">
-        <v>0.0823203403226071</v>
+        <v>0.0500002702853112</v>
       </c>
       <c r="D636" t="n">
         <v>0</v>
       </c>
       <c r="E636" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F636" t="s">
         <v>104</v>
@@ -28651,7 +28648,7 @@
         <v>15</v>
       </c>
       <c r="L636" t="n">
-        <v>8.23</v>
+        <v>5</v>
       </c>
       <c r="M636" t="n">
         <v>0</v>
@@ -28665,13 +28662,13 @@
         <v>63</v>
       </c>
       <c r="C637" t="n">
-        <v>0.0552025039821992</v>
+        <v>0.0823203403226071</v>
       </c>
       <c r="D637" t="n">
         <v>0</v>
       </c>
       <c r="E637" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F637" t="s">
         <v>104</v>
@@ -28692,7 +28689,7 @@
         <v>15</v>
       </c>
       <c r="L637" t="n">
-        <v>5.52</v>
+        <v>8.23</v>
       </c>
       <c r="M637" t="n">
         <v>0</v>
@@ -28706,13 +28703,13 @@
         <v>63</v>
       </c>
       <c r="C638" t="n">
-        <v>0.0763997056178605</v>
+        <v>0.0552025039821992</v>
       </c>
       <c r="D638" t="n">
         <v>0</v>
       </c>
       <c r="E638" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F638" t="s">
         <v>104</v>
@@ -28733,7 +28730,7 @@
         <v>15</v>
       </c>
       <c r="L638" t="n">
-        <v>7.64</v>
+        <v>5.52</v>
       </c>
       <c r="M638" t="n">
         <v>0</v>
@@ -28747,13 +28744,13 @@
         <v>63</v>
       </c>
       <c r="C639" t="n">
-        <v>0.0511630210291621</v>
+        <v>0.0763997056178605</v>
       </c>
       <c r="D639" t="n">
         <v>0</v>
       </c>
       <c r="E639" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F639" t="s">
         <v>104</v>
@@ -28774,7 +28771,7 @@
         <v>15</v>
       </c>
       <c r="L639" t="n">
-        <v>5.12</v>
+        <v>7.64</v>
       </c>
       <c r="M639" t="n">
         <v>0</v>
@@ -28788,13 +28785,13 @@
         <v>63</v>
       </c>
       <c r="C640" t="n">
-        <v>0.0521750465383623</v>
+        <v>0.0511630210291621</v>
       </c>
       <c r="D640" t="n">
         <v>0</v>
       </c>
       <c r="E640" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F640" t="s">
         <v>104</v>
@@ -28815,7 +28812,7 @@
         <v>15</v>
       </c>
       <c r="L640" t="n">
-        <v>5.22</v>
+        <v>5.12</v>
       </c>
       <c r="M640" t="n">
         <v>0</v>
@@ -28829,13 +28826,13 @@
         <v>63</v>
       </c>
       <c r="C641" t="n">
-        <v>0.0587567689865834</v>
+        <v>0.0521750465383623</v>
       </c>
       <c r="D641" t="n">
         <v>0</v>
       </c>
       <c r="E641" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F641" t="s">
         <v>104</v>
@@ -28856,7 +28853,7 @@
         <v>15</v>
       </c>
       <c r="L641" t="n">
-        <v>5.88</v>
+        <v>5.22</v>
       </c>
       <c r="M641" t="n">
         <v>0</v>
@@ -28870,13 +28867,13 @@
         <v>63</v>
       </c>
       <c r="C642" t="n">
-        <v>0.0745280846023219</v>
+        <v>0.0587567689865834</v>
       </c>
       <c r="D642" t="n">
         <v>0</v>
       </c>
       <c r="E642" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F642" t="s">
         <v>104</v>
@@ -28897,7 +28894,7 @@
         <v>15</v>
       </c>
       <c r="L642" t="n">
-        <v>7.45</v>
+        <v>5.88</v>
       </c>
       <c r="M642" t="n">
         <v>0</v>
@@ -28911,7 +28908,7 @@
         <v>63</v>
       </c>
       <c r="C643" t="n">
-        <v>0.0517636085066878</v>
+        <v>0.0745280846023219</v>
       </c>
       <c r="D643" t="n">
         <v>0</v>
@@ -28938,7 +28935,7 @@
         <v>15</v>
       </c>
       <c r="L643" t="n">
-        <v>5.18</v>
+        <v>7.45</v>
       </c>
       <c r="M643" t="n">
         <v>0</v>
@@ -28952,13 +28949,13 @@
         <v>63</v>
       </c>
       <c r="C644" t="n">
-        <v>0.0610178454135785</v>
+        <v>0.0517636085066878</v>
       </c>
       <c r="D644" t="n">
         <v>0</v>
       </c>
       <c r="E644" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F644" t="s">
         <v>104</v>
@@ -28979,7 +28976,7 @@
         <v>15</v>
       </c>
       <c r="L644" t="n">
-        <v>6.1</v>
+        <v>5.18</v>
       </c>
       <c r="M644" t="n">
         <v>0</v>
@@ -28993,13 +28990,13 @@
         <v>63</v>
       </c>
       <c r="C645" t="n">
-        <v>0.0606131315597566</v>
+        <v>0.0610178454135785</v>
       </c>
       <c r="D645" t="n">
         <v>0</v>
       </c>
       <c r="E645" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F645" t="s">
         <v>104</v>
@@ -29020,7 +29017,7 @@
         <v>15</v>
       </c>
       <c r="L645" t="n">
-        <v>6.06</v>
+        <v>6.1</v>
       </c>
       <c r="M645" t="n">
         <v>0</v>
@@ -29031,37 +29028,37 @@
         <v>684</v>
       </c>
       <c r="B646" t="n">
-        <v>651</v>
+        <v>63</v>
       </c>
       <c r="C646" t="n">
-        <v>0.0568868121607993</v>
+        <v>0.0606131315597566</v>
       </c>
       <c r="D646" t="n">
         <v>0</v>
       </c>
       <c r="E646" t="n">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="F646" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="G646" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H646" t="s">
         <v>15</v>
       </c>
       <c r="I646" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J646" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K646" t="s">
         <v>15</v>
       </c>
       <c r="L646" t="n">
-        <v>5.69</v>
+        <v>6.06</v>
       </c>
       <c r="M646" t="n">
         <v>0</v>
@@ -29072,37 +29069,37 @@
         <v>685</v>
       </c>
       <c r="B647" t="n">
-        <v>715</v>
+        <v>651</v>
       </c>
       <c r="C647" t="n">
-        <v>0.0592449407564614</v>
+        <v>0.0568868121607993</v>
       </c>
       <c r="D647" t="n">
         <v>0</v>
       </c>
       <c r="E647" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="F647" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="G647" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H647" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I647" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J647" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K647" t="s">
         <v>15</v>
       </c>
       <c r="L647" t="n">
-        <v>5.92</v>
+        <v>5.69</v>
       </c>
       <c r="M647" t="n">
         <v>0</v>
@@ -29116,13 +29113,13 @@
         <v>715</v>
       </c>
       <c r="C648" t="n">
-        <v>0.0532439900846185</v>
+        <v>0.0592449407564614</v>
       </c>
       <c r="D648" t="n">
         <v>0</v>
       </c>
       <c r="E648" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F648" t="s">
         <v>127</v>
@@ -29143,7 +29140,7 @@
         <v>15</v>
       </c>
       <c r="L648" t="n">
-        <v>5.32</v>
+        <v>5.92</v>
       </c>
       <c r="M648" t="n">
         <v>0</v>
@@ -29157,7 +29154,7 @@
         <v>715</v>
       </c>
       <c r="C649" t="n">
-        <v>0.0515018489527881</v>
+        <v>0.0532439900846185</v>
       </c>
       <c r="D649" t="n">
         <v>0</v>
@@ -29184,7 +29181,7 @@
         <v>15</v>
       </c>
       <c r="L649" t="n">
-        <v>5.15</v>
+        <v>5.32</v>
       </c>
       <c r="M649" t="n">
         <v>0</v>
@@ -29195,37 +29192,37 @@
         <v>688</v>
       </c>
       <c r="B650" t="n">
-        <v>753</v>
+        <v>715</v>
       </c>
       <c r="C650" t="n">
-        <v>0.0562382346788196</v>
+        <v>0.0515018489527881</v>
       </c>
       <c r="D650" t="n">
         <v>0</v>
       </c>
       <c r="E650" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F650" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="G650" t="s">
         <v>20</v>
       </c>
       <c r="H650" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I650" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J650" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K650" t="s">
         <v>15</v>
       </c>
       <c r="L650" t="n">
-        <v>5.62</v>
+        <v>5.15</v>
       </c>
       <c r="M650" t="n">
         <v>0</v>
@@ -29239,7 +29236,7 @@
         <v>753</v>
       </c>
       <c r="C651" t="n">
-        <v>0.0684786553815663</v>
+        <v>0.0562382346788196</v>
       </c>
       <c r="D651" t="n">
         <v>0</v>
@@ -29266,7 +29263,7 @@
         <v>15</v>
       </c>
       <c r="L651" t="n">
-        <v>6.85</v>
+        <v>5.62</v>
       </c>
       <c r="M651" t="n">
         <v>0</v>
@@ -29280,7 +29277,7 @@
         <v>753</v>
       </c>
       <c r="C652" t="n">
-        <v>0.122558530135046</v>
+        <v>0.0684786553815663</v>
       </c>
       <c r="D652" t="n">
         <v>0</v>
@@ -29307,7 +29304,7 @@
         <v>15</v>
       </c>
       <c r="L652" t="n">
-        <v>12.26</v>
+        <v>6.85</v>
       </c>
       <c r="M652" t="n">
         <v>0</v>
@@ -29321,7 +29318,7 @@
         <v>753</v>
       </c>
       <c r="C653" t="n">
-        <v>0.0828118014047018</v>
+        <v>0.122558530135046</v>
       </c>
       <c r="D653" t="n">
         <v>0</v>
@@ -29348,7 +29345,7 @@
         <v>15</v>
       </c>
       <c r="L653" t="n">
-        <v>8.28</v>
+        <v>12.26</v>
       </c>
       <c r="M653" t="n">
         <v>0</v>
@@ -29362,7 +29359,7 @@
         <v>753</v>
       </c>
       <c r="C654" t="n">
-        <v>0.0502883283289919</v>
+        <v>0.0828118014047018</v>
       </c>
       <c r="D654" t="n">
         <v>0</v>
@@ -29389,7 +29386,7 @@
         <v>15</v>
       </c>
       <c r="L654" t="n">
-        <v>5.03</v>
+        <v>8.28</v>
       </c>
       <c r="M654" t="n">
         <v>0</v>
@@ -29400,22 +29397,22 @@
         <v>693</v>
       </c>
       <c r="B655" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C655" t="n">
-        <v>0.0533584737829077</v>
+        <v>0.0502883283289919</v>
       </c>
       <c r="D655" t="n">
         <v>0</v>
       </c>
       <c r="E655" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F655" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G655" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H655" t="s">
         <v>15</v>
@@ -29424,13 +29421,13 @@
         <v>46</v>
       </c>
       <c r="J655" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K655" t="s">
         <v>15</v>
       </c>
       <c r="L655" t="n">
-        <v>5.34</v>
+        <v>5.03</v>
       </c>
       <c r="M655" t="n">
         <v>0</v>
@@ -29441,19 +29438,19 @@
         <v>694</v>
       </c>
       <c r="B656" t="n">
-        <v>813</v>
+        <v>755</v>
       </c>
       <c r="C656" t="n">
-        <v>0.0519629820558511</v>
+        <v>0.0533584737829077</v>
       </c>
       <c r="D656" t="n">
         <v>0</v>
       </c>
       <c r="E656" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F656" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G656" t="s">
         <v>15</v>
@@ -29462,16 +29459,16 @@
         <v>15</v>
       </c>
       <c r="I656" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J656" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K656" t="s">
         <v>15</v>
       </c>
       <c r="L656" t="n">
-        <v>5.2</v>
+        <v>5.34</v>
       </c>
       <c r="M656" t="n">
         <v>0</v>
@@ -29485,13 +29482,13 @@
         <v>813</v>
       </c>
       <c r="C657" t="n">
-        <v>0.0510167725040024</v>
+        <v>0.0519629820558511</v>
       </c>
       <c r="D657" t="n">
         <v>0</v>
       </c>
       <c r="E657" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="F657" t="s">
         <v>104</v>
@@ -29512,7 +29509,7 @@
         <v>15</v>
       </c>
       <c r="L657" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M657" t="n">
         <v>0</v>
@@ -29526,16 +29523,16 @@
         <v>813</v>
       </c>
       <c r="C658" t="n">
-        <v>0.0518902080201361</v>
+        <v>0.0510167725040024</v>
       </c>
       <c r="D658" t="n">
         <v>0</v>
       </c>
       <c r="E658" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F658" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G658" t="s">
         <v>15</v>
@@ -29553,7 +29550,7 @@
         <v>15</v>
       </c>
       <c r="L658" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
       <c r="M658" t="n">
         <v>0</v>
@@ -29564,19 +29561,19 @@
         <v>697</v>
       </c>
       <c r="B659" t="n">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C659" t="n">
-        <v>0.0806049797518489</v>
+        <v>0.0518902080201361</v>
       </c>
       <c r="D659" t="n">
         <v>0</v>
       </c>
       <c r="E659" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F659" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G659" t="s">
         <v>15</v>
@@ -29585,7 +29582,7 @@
         <v>15</v>
       </c>
       <c r="I659" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="J659" t="s">
         <v>17</v>
@@ -29594,7 +29591,7 @@
         <v>15</v>
       </c>
       <c r="L659" t="n">
-        <v>8.06</v>
+        <v>5.19</v>
       </c>
       <c r="M659" t="n">
         <v>0</v>
@@ -29608,13 +29605,13 @@
         <v>816</v>
       </c>
       <c r="C660" t="n">
-        <v>0.056330759788897</v>
+        <v>0.0806049797518489</v>
       </c>
       <c r="D660" t="n">
         <v>0</v>
       </c>
       <c r="E660" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F660" t="s">
         <v>26</v>
@@ -29635,7 +29632,7 @@
         <v>15</v>
       </c>
       <c r="L660" t="n">
-        <v>5.63</v>
+        <v>8.06</v>
       </c>
       <c r="M660" t="n">
         <v>0</v>
@@ -29646,10 +29643,10 @@
         <v>699</v>
       </c>
       <c r="B661" t="n">
-        <v>83</v>
+        <v>816</v>
       </c>
       <c r="C661" t="n">
-        <v>0.0608275230817745</v>
+        <v>0.056330759788897</v>
       </c>
       <c r="D661" t="n">
         <v>0</v>
@@ -29658,25 +29655,25 @@
         <v>5</v>
       </c>
       <c r="F661" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G661" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H661" t="s">
         <v>15</v>
       </c>
       <c r="I661" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J661" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K661" t="s">
         <v>15</v>
       </c>
       <c r="L661" t="n">
-        <v>6.08</v>
+        <v>5.63</v>
       </c>
       <c r="M661" t="n">
         <v>0</v>
@@ -29690,13 +29687,13 @@
         <v>83</v>
       </c>
       <c r="C662" t="n">
-        <v>0.0500326649576064</v>
+        <v>0.0608275230817745</v>
       </c>
       <c r="D662" t="n">
         <v>0</v>
       </c>
       <c r="E662" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F662" t="s">
         <v>104</v>
@@ -29717,7 +29714,7 @@
         <v>15</v>
       </c>
       <c r="L662" t="n">
-        <v>5</v>
+        <v>6.08</v>
       </c>
       <c r="M662" t="n">
         <v>0</v>
@@ -29728,16 +29725,16 @@
         <v>701</v>
       </c>
       <c r="B663" t="n">
-        <v>847</v>
+        <v>83</v>
       </c>
       <c r="C663" t="n">
-        <v>0.133515685974933</v>
+        <v>0.0500326649576064</v>
       </c>
       <c r="D663" t="n">
         <v>0</v>
       </c>
       <c r="E663" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F663" t="s">
         <v>104</v>
@@ -29758,7 +29755,7 @@
         <v>15</v>
       </c>
       <c r="L663" t="n">
-        <v>13.35</v>
+        <v>5</v>
       </c>
       <c r="M663" t="n">
         <v>0</v>
@@ -29772,16 +29769,16 @@
         <v>847</v>
       </c>
       <c r="C664" t="n">
-        <v>0.384114466603136</v>
+        <v>0.133515685974933</v>
       </c>
       <c r="D664" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E664" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F664" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G664" t="s">
         <v>20</v>
@@ -29799,10 +29796,10 @@
         <v>15</v>
       </c>
       <c r="L664" t="n">
-        <v>38.41</v>
+        <v>13.35</v>
       </c>
       <c r="M664" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="665">
@@ -29810,19 +29807,19 @@
         <v>703</v>
       </c>
       <c r="B665" t="n">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C665" t="n">
-        <v>0.0787102493105438</v>
+        <v>0.384114466603136</v>
       </c>
       <c r="D665" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E665" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F665" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="G665" t="s">
         <v>20</v>
@@ -29831,7 +29828,7 @@
         <v>15</v>
       </c>
       <c r="I665" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J665" t="s">
         <v>22</v>
@@ -29840,10 +29837,10 @@
         <v>15</v>
       </c>
       <c r="L665" t="n">
-        <v>7.87</v>
+        <v>38.41</v>
       </c>
       <c r="M665" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="666">
@@ -29854,13 +29851,13 @@
         <v>849</v>
       </c>
       <c r="C666" t="n">
-        <v>0.0500071368982664</v>
+        <v>0.0787102493105438</v>
       </c>
       <c r="D666" t="n">
         <v>0</v>
       </c>
       <c r="E666" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F666" t="s">
         <v>100</v>
@@ -29881,7 +29878,7 @@
         <v>15</v>
       </c>
       <c r="L666" t="n">
-        <v>5</v>
+        <v>7.87</v>
       </c>
       <c r="M666" t="n">
         <v>0</v>
@@ -29895,13 +29892,13 @@
         <v>849</v>
       </c>
       <c r="C667" t="n">
-        <v>0.0572216058902983</v>
+        <v>0.0500071368982664</v>
       </c>
       <c r="D667" t="n">
         <v>0</v>
       </c>
       <c r="E667" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F667" t="s">
         <v>100</v>
@@ -29922,7 +29919,7 @@
         <v>15</v>
       </c>
       <c r="L667" t="n">
-        <v>5.72</v>
+        <v>5</v>
       </c>
       <c r="M667" t="n">
         <v>0</v>
@@ -29933,19 +29930,19 @@
         <v>706</v>
       </c>
       <c r="B668" t="n">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C668" t="n">
-        <v>0.112456862233724</v>
+        <v>0.0572216058902983</v>
       </c>
       <c r="D668" t="n">
         <v>0</v>
       </c>
       <c r="E668" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F668" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="G668" t="s">
         <v>20</v>
@@ -29954,7 +29951,7 @@
         <v>15</v>
       </c>
       <c r="I668" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J668" t="s">
         <v>22</v>
@@ -29963,7 +29960,7 @@
         <v>15</v>
       </c>
       <c r="L668" t="n">
-        <v>11.25</v>
+        <v>5.72</v>
       </c>
       <c r="M668" t="n">
         <v>0</v>
@@ -29977,7 +29974,7 @@
         <v>850</v>
       </c>
       <c r="C669" t="n">
-        <v>0.0500514100343107</v>
+        <v>0.112456862233724</v>
       </c>
       <c r="D669" t="n">
         <v>0</v>
@@ -29986,7 +29983,7 @@
         <v>6</v>
       </c>
       <c r="F669" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="G669" t="s">
         <v>20</v>
@@ -30004,7 +30001,7 @@
         <v>15</v>
       </c>
       <c r="L669" t="n">
-        <v>5.01</v>
+        <v>11.25</v>
       </c>
       <c r="M669" t="n">
         <v>0</v>
@@ -30015,19 +30012,19 @@
         <v>708</v>
       </c>
       <c r="B670" t="n">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C670" t="n">
-        <v>0.137503805617554</v>
+        <v>0.0500514100343107</v>
       </c>
       <c r="D670" t="n">
         <v>0</v>
       </c>
       <c r="E670" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F670" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="G670" t="s">
         <v>20</v>
@@ -30036,7 +30033,7 @@
         <v>15</v>
       </c>
       <c r="I670" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J670" t="s">
         <v>22</v>
@@ -30045,7 +30042,7 @@
         <v>15</v>
       </c>
       <c r="L670" t="n">
-        <v>13.75</v>
+        <v>5.01</v>
       </c>
       <c r="M670" t="n">
         <v>0</v>
@@ -30059,13 +30056,13 @@
         <v>855</v>
       </c>
       <c r="C671" t="n">
-        <v>0.0504968263326432</v>
+        <v>0.137503805617554</v>
       </c>
       <c r="D671" t="n">
         <v>0</v>
       </c>
       <c r="E671" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F671" t="s">
         <v>33</v>
@@ -30086,7 +30083,7 @@
         <v>15</v>
       </c>
       <c r="L671" t="n">
-        <v>5.05</v>
+        <v>13.75</v>
       </c>
       <c r="M671" t="n">
         <v>0</v>
@@ -30100,13 +30097,13 @@
         <v>855</v>
       </c>
       <c r="C672" t="n">
-        <v>0.0515273519614271</v>
+        <v>0.0504968263326432</v>
       </c>
       <c r="D672" t="n">
         <v>0</v>
       </c>
       <c r="E672" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F672" t="s">
         <v>33</v>
@@ -30127,7 +30124,7 @@
         <v>15</v>
       </c>
       <c r="L672" t="n">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="M672" t="n">
         <v>0</v>
@@ -30141,13 +30138,13 @@
         <v>855</v>
       </c>
       <c r="C673" t="n">
-        <v>0.0619058220039127</v>
+        <v>0.0515273519614271</v>
       </c>
       <c r="D673" t="n">
         <v>0</v>
       </c>
       <c r="E673" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F673" t="s">
         <v>33</v>
@@ -30168,7 +30165,7 @@
         <v>15</v>
       </c>
       <c r="L673" t="n">
-        <v>6.19</v>
+        <v>5.15</v>
       </c>
       <c r="M673" t="n">
         <v>0</v>
@@ -30179,19 +30176,19 @@
         <v>712</v>
       </c>
       <c r="B674" t="n">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="C674" t="n">
-        <v>0.0500001605117539</v>
+        <v>0.0619058220039127</v>
       </c>
       <c r="D674" t="n">
         <v>0</v>
       </c>
       <c r="E674" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F674" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G674" t="s">
         <v>20</v>
@@ -30200,7 +30197,7 @@
         <v>15</v>
       </c>
       <c r="I674" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J674" t="s">
         <v>22</v>
@@ -30209,7 +30206,7 @@
         <v>15</v>
       </c>
       <c r="L674" t="n">
-        <v>5</v>
+        <v>6.19</v>
       </c>
       <c r="M674" t="n">
         <v>0</v>
@@ -30223,13 +30220,13 @@
         <v>871</v>
       </c>
       <c r="C675" t="n">
-        <v>0.0670061113355102</v>
+        <v>0.0500001605117539</v>
       </c>
       <c r="D675" t="n">
         <v>0</v>
       </c>
       <c r="E675" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F675" t="s">
         <v>24</v>
@@ -30250,7 +30247,7 @@
         <v>15</v>
       </c>
       <c r="L675" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="M675" t="n">
         <v>0</v>
@@ -30264,13 +30261,13 @@
         <v>871</v>
       </c>
       <c r="C676" t="n">
-        <v>0.0500099870452234</v>
+        <v>0.0670061113355102</v>
       </c>
       <c r="D676" t="n">
         <v>0</v>
       </c>
       <c r="E676" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F676" t="s">
         <v>24</v>
@@ -30291,7 +30288,7 @@
         <v>15</v>
       </c>
       <c r="L676" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="M676" t="n">
         <v>0</v>
@@ -30302,37 +30299,37 @@
         <v>715</v>
       </c>
       <c r="B677" t="n">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="C677" t="n">
-        <v>0.0511701183959265</v>
+        <v>0.0500099870452234</v>
       </c>
       <c r="D677" t="n">
         <v>0</v>
       </c>
       <c r="E677" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F677" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G677" t="s">
         <v>20</v>
       </c>
       <c r="H677" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I677" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J677" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K677" t="s">
         <v>15</v>
       </c>
       <c r="L677" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="M677" t="n">
         <v>0</v>
@@ -30346,13 +30343,13 @@
         <v>877</v>
       </c>
       <c r="C678" t="n">
-        <v>0.0500153023918106</v>
+        <v>0.0511701183959265</v>
       </c>
       <c r="D678" t="n">
         <v>0</v>
       </c>
       <c r="E678" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F678" t="s">
         <v>33</v>
@@ -30373,7 +30370,7 @@
         <v>15</v>
       </c>
       <c r="L678" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="M678" t="n">
         <v>0</v>
@@ -30384,37 +30381,37 @@
         <v>717</v>
       </c>
       <c r="B679" t="n">
-        <v>908</v>
+        <v>877</v>
       </c>
       <c r="C679" t="n">
-        <v>0.0873965358374162</v>
+        <v>0.0500153023918106</v>
       </c>
       <c r="D679" t="n">
         <v>0</v>
       </c>
       <c r="E679" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F679" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="G679" t="s">
         <v>20</v>
       </c>
       <c r="H679" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I679" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J679" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K679" t="s">
         <v>15</v>
       </c>
       <c r="L679" t="n">
-        <v>8.74</v>
+        <v>5</v>
       </c>
       <c r="M679" t="n">
         <v>0</v>
@@ -30425,19 +30422,19 @@
         <v>718</v>
       </c>
       <c r="B680" t="n">
-        <v>91</v>
+        <v>908</v>
       </c>
       <c r="C680" t="n">
-        <v>1</v>
+        <v>0.0873965358374162</v>
       </c>
       <c r="D680" t="n">
-        <v>0.734615384615385</v>
+        <v>0</v>
       </c>
       <c r="E680" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F680" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="G680" t="s">
         <v>20</v>
@@ -30449,16 +30446,16 @@
         <v>21</v>
       </c>
       <c r="J680" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K680" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L680" t="n">
-        <v>100</v>
+        <v>8.74</v>
       </c>
       <c r="M680" t="n">
-        <v>73.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="681">
@@ -30469,13 +30466,13 @@
         <v>91</v>
       </c>
       <c r="C681" t="n">
-        <v>0.888399159680283</v>
+        <v>1</v>
       </c>
       <c r="D681" t="n">
-        <v>0.51077943615257</v>
+        <v>0.734615384615385</v>
       </c>
       <c r="E681" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="F681" t="s">
         <v>26</v>
@@ -30496,10 +30493,10 @@
         <v>20</v>
       </c>
       <c r="L681" t="n">
-        <v>88.84</v>
+        <v>100</v>
       </c>
       <c r="M681" t="n">
-        <v>51.08</v>
+        <v>73.46</v>
       </c>
     </row>
     <row r="682">
@@ -30510,13 +30507,13 @@
         <v>91</v>
       </c>
       <c r="C682" t="n">
-        <v>1</v>
+        <v>0.888399159680283</v>
       </c>
       <c r="D682" t="n">
-        <v>0.970588235294118</v>
+        <v>0.51077943615257</v>
       </c>
       <c r="E682" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F682" t="s">
         <v>26</v>
@@ -30537,10 +30534,10 @@
         <v>20</v>
       </c>
       <c r="L682" t="n">
-        <v>100</v>
+        <v>88.84</v>
       </c>
       <c r="M682" t="n">
-        <v>97.06</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="683">
@@ -30554,10 +30551,10 @@
         <v>1</v>
       </c>
       <c r="D683" t="n">
-        <v>0.580645161290323</v>
+        <v>0.970588235294118</v>
       </c>
       <c r="E683" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="F683" t="s">
         <v>26</v>
@@ -30581,7 +30578,7 @@
         <v>100</v>
       </c>
       <c r="M683" t="n">
-        <v>58.06</v>
+        <v>97.06</v>
       </c>
     </row>
     <row r="684">
@@ -30592,13 +30589,13 @@
         <v>91</v>
       </c>
       <c r="C684" t="n">
-        <v>0.999999999957086</v>
+        <v>1</v>
       </c>
       <c r="D684" t="n">
-        <v>0.675824175824176</v>
+        <v>0.580645161290323</v>
       </c>
       <c r="E684" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F684" t="s">
         <v>26</v>
@@ -30622,7 +30619,7 @@
         <v>100</v>
       </c>
       <c r="M684" t="n">
-        <v>67.58</v>
+        <v>58.06</v>
       </c>
     </row>
     <row r="685">
@@ -30633,13 +30630,13 @@
         <v>91</v>
       </c>
       <c r="C685" t="n">
-        <v>0.999999733353755</v>
+        <v>0.999999999957086</v>
       </c>
       <c r="D685" t="n">
-        <v>0.717557251908397</v>
+        <v>0.675824175824176</v>
       </c>
       <c r="E685" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F685" t="s">
         <v>26</v>
@@ -30663,7 +30660,7 @@
         <v>100</v>
       </c>
       <c r="M685" t="n">
-        <v>71.76</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="686">
@@ -30674,13 +30671,13 @@
         <v>91</v>
       </c>
       <c r="C686" t="n">
-        <v>1</v>
+        <v>0.999999733353755</v>
       </c>
       <c r="D686" t="n">
-        <v>0.833333333333333</v>
+        <v>0.717557251908397</v>
       </c>
       <c r="E686" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F686" t="s">
         <v>26</v>
@@ -30704,7 +30701,7 @@
         <v>100</v>
       </c>
       <c r="M686" t="n">
-        <v>83.33</v>
+        <v>71.76</v>
       </c>
     </row>
     <row r="687">
@@ -30715,13 +30712,13 @@
         <v>91</v>
       </c>
       <c r="C687" t="n">
-        <v>0.933191106636875</v>
+        <v>1</v>
       </c>
       <c r="D687" t="n">
-        <v>0.555555555555556</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E687" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F687" t="s">
         <v>26</v>
@@ -30742,10 +30739,10 @@
         <v>20</v>
       </c>
       <c r="L687" t="n">
-        <v>93.32</v>
+        <v>100</v>
       </c>
       <c r="M687" t="n">
-        <v>55.56</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="688">
@@ -30756,13 +30753,13 @@
         <v>91</v>
       </c>
       <c r="C688" t="n">
-        <v>1</v>
+        <v>0.933191106636875</v>
       </c>
       <c r="D688" t="n">
-        <v>0.80791788856305</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="E688" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="F688" t="s">
         <v>26</v>
@@ -30783,10 +30780,10 @@
         <v>20</v>
       </c>
       <c r="L688" t="n">
-        <v>100</v>
+        <v>93.32</v>
       </c>
       <c r="M688" t="n">
-        <v>80.79</v>
+        <v>55.56</v>
       </c>
     </row>
     <row r="689">
@@ -30797,13 +30794,13 @@
         <v>91</v>
       </c>
       <c r="C689" t="n">
-        <v>0.969429828932395</v>
+        <v>1</v>
       </c>
       <c r="D689" t="n">
-        <v>0.6875</v>
+        <v>0.80791788856305</v>
       </c>
       <c r="E689" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="F689" t="s">
         <v>26</v>
@@ -30824,10 +30821,10 @@
         <v>20</v>
       </c>
       <c r="L689" t="n">
-        <v>96.94</v>
+        <v>100</v>
       </c>
       <c r="M689" t="n">
-        <v>68.75</v>
+        <v>80.79</v>
       </c>
     </row>
     <row r="690">
@@ -30838,13 +30835,13 @@
         <v>91</v>
       </c>
       <c r="C690" t="n">
-        <v>0.935002182893151</v>
+        <v>0.969429828932395</v>
       </c>
       <c r="D690" t="n">
-        <v>0.511627906976744</v>
+        <v>0.6875</v>
       </c>
       <c r="E690" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F690" t="s">
         <v>26</v>
@@ -30865,10 +30862,10 @@
         <v>20</v>
       </c>
       <c r="L690" t="n">
-        <v>93.5</v>
+        <v>96.94</v>
       </c>
       <c r="M690" t="n">
-        <v>51.16</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="691">
@@ -30879,13 +30876,13 @@
         <v>91</v>
       </c>
       <c r="C691" t="n">
-        <v>1</v>
+        <v>0.935002182893151</v>
       </c>
       <c r="D691" t="n">
-        <v>0.993506493506494</v>
+        <v>0.511627906976744</v>
       </c>
       <c r="E691" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F691" t="s">
         <v>26</v>
@@ -30906,10 +30903,10 @@
         <v>20</v>
       </c>
       <c r="L691" t="n">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="M691" t="n">
-        <v>99.35</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="692">
@@ -30917,19 +30914,19 @@
         <v>730</v>
       </c>
       <c r="B692" t="n">
-        <v>912</v>
+        <v>91</v>
       </c>
       <c r="C692" t="n">
-        <v>0.104065133446721</v>
+        <v>1</v>
       </c>
       <c r="D692" t="n">
-        <v>0</v>
+        <v>0.993506493506494</v>
       </c>
       <c r="E692" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F692" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="G692" t="s">
         <v>20</v>
@@ -30938,19 +30935,19 @@
         <v>15</v>
       </c>
       <c r="I692" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J692" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K692" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L692" t="n">
-        <v>10.41</v>
+        <v>100</v>
       </c>
       <c r="M692" t="n">
-        <v>0</v>
+        <v>99.35</v>
       </c>
     </row>
     <row r="693">
@@ -30961,13 +30958,13 @@
         <v>912</v>
       </c>
       <c r="C693" t="n">
-        <v>0.230314184577067</v>
+        <v>0.104065133446721</v>
       </c>
       <c r="D693" t="n">
-        <v>0.0792079207920792</v>
+        <v>0</v>
       </c>
       <c r="E693" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F693" t="s">
         <v>129</v>
@@ -30988,10 +30985,10 @@
         <v>15</v>
       </c>
       <c r="L693" t="n">
-        <v>23.03</v>
+        <v>10.41</v>
       </c>
       <c r="M693" t="n">
-        <v>7.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="694">
@@ -30999,19 +30996,19 @@
         <v>732</v>
       </c>
       <c r="B694" t="n">
-        <v>936</v>
+        <v>912</v>
       </c>
       <c r="C694" t="n">
-        <v>0.0500713172709876</v>
+        <v>0.230314184577067</v>
       </c>
       <c r="D694" t="n">
-        <v>0</v>
+        <v>0.0792079207920792</v>
       </c>
       <c r="E694" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F694" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="G694" t="s">
         <v>20</v>
@@ -31020,7 +31017,7 @@
         <v>15</v>
       </c>
       <c r="I694" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J694" t="s">
         <v>22</v>
@@ -31029,10 +31026,10 @@
         <v>15</v>
       </c>
       <c r="L694" t="n">
-        <v>5.01</v>
+        <v>23.03</v>
       </c>
       <c r="M694" t="n">
-        <v>0</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="695">
@@ -31043,13 +31040,13 @@
         <v>936</v>
       </c>
       <c r="C695" t="n">
-        <v>0.0503565947948979</v>
+        <v>0.0500713172709876</v>
       </c>
       <c r="D695" t="n">
-        <v>0.0204081632653061</v>
+        <v>0</v>
       </c>
       <c r="E695" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F695" t="s">
         <v>90</v>
@@ -31070,10 +31067,10 @@
         <v>15</v>
       </c>
       <c r="L695" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
       <c r="M695" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="696">
@@ -31084,16 +31081,16 @@
         <v>936</v>
       </c>
       <c r="C696" t="n">
-        <v>0.0535225272094203</v>
+        <v>0.0503565947948979</v>
       </c>
       <c r="D696" t="n">
-        <v>0</v>
+        <v>0.0204081632653061</v>
       </c>
       <c r="E696" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F696" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G696" t="s">
         <v>20</v>
@@ -31111,10 +31108,10 @@
         <v>15</v>
       </c>
       <c r="L696" t="n">
-        <v>5.35</v>
+        <v>5.04</v>
       </c>
       <c r="M696" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="697">
@@ -31122,19 +31119,19 @@
         <v>735</v>
       </c>
       <c r="B697" t="n">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="C697" t="n">
-        <v>0.0523022495166284</v>
+        <v>0.0535225272094203</v>
       </c>
       <c r="D697" t="n">
         <v>0</v>
       </c>
       <c r="E697" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F697" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="G697" t="s">
         <v>20</v>
@@ -31143,7 +31140,7 @@
         <v>15</v>
       </c>
       <c r="I697" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J697" t="s">
         <v>22</v>
@@ -31152,7 +31149,7 @@
         <v>15</v>
       </c>
       <c r="L697" t="n">
-        <v>5.23</v>
+        <v>5.35</v>
       </c>
       <c r="M697" t="n">
         <v>0</v>
@@ -31166,13 +31163,13 @@
         <v>939</v>
       </c>
       <c r="C698" t="n">
-        <v>0.0501423283500585</v>
+        <v>0.0523022495166284</v>
       </c>
       <c r="D698" t="n">
         <v>0</v>
       </c>
       <c r="E698" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F698" t="s">
         <v>14</v>
@@ -31193,7 +31190,7 @@
         <v>15</v>
       </c>
       <c r="L698" t="n">
-        <v>5.01</v>
+        <v>5.23</v>
       </c>
       <c r="M698" t="n">
         <v>0</v>
@@ -31204,19 +31201,19 @@
         <v>737</v>
       </c>
       <c r="B699" t="n">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="C699" t="n">
-        <v>0.0764509114539819</v>
+        <v>0.0501423283500585</v>
       </c>
       <c r="D699" t="n">
-        <v>0.0769230769230769</v>
+        <v>0</v>
       </c>
       <c r="E699" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F699" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="G699" t="s">
         <v>20</v>
@@ -31225,7 +31222,7 @@
         <v>15</v>
       </c>
       <c r="I699" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J699" t="s">
         <v>22</v>
@@ -31234,10 +31231,10 @@
         <v>15</v>
       </c>
       <c r="L699" t="n">
-        <v>7.65</v>
+        <v>5.01</v>
       </c>
       <c r="M699" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="700">
@@ -31248,13 +31245,13 @@
         <v>952</v>
       </c>
       <c r="C700" t="n">
-        <v>0.0607319644423374</v>
+        <v>0.0764509114539819</v>
       </c>
       <c r="D700" t="n">
-        <v>0</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="E700" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F700" t="s">
         <v>100</v>
@@ -31275,10 +31272,10 @@
         <v>15</v>
       </c>
       <c r="L700" t="n">
-        <v>6.07</v>
+        <v>7.65</v>
       </c>
       <c r="M700" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="701">
@@ -31289,13 +31286,13 @@
         <v>952</v>
       </c>
       <c r="C701" t="n">
-        <v>0.06878906329815</v>
+        <v>0.0607319644423374</v>
       </c>
       <c r="D701" t="n">
         <v>0</v>
       </c>
       <c r="E701" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F701" t="s">
         <v>100</v>
@@ -31316,7 +31313,7 @@
         <v>15</v>
       </c>
       <c r="L701" t="n">
-        <v>6.88</v>
+        <v>6.07</v>
       </c>
       <c r="M701" t="n">
         <v>0</v>
@@ -31327,19 +31324,19 @@
         <v>740</v>
       </c>
       <c r="B702" t="n">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="C702" t="n">
-        <v>0.0502277251458878</v>
+        <v>0.06878906329815</v>
       </c>
       <c r="D702" t="n">
         <v>0</v>
       </c>
       <c r="E702" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F702" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G702" t="s">
         <v>20</v>
@@ -31348,7 +31345,7 @@
         <v>15</v>
       </c>
       <c r="I702" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J702" t="s">
         <v>22</v>
@@ -31357,7 +31354,7 @@
         <v>15</v>
       </c>
       <c r="L702" t="n">
-        <v>5.02</v>
+        <v>6.88</v>
       </c>
       <c r="M702" t="n">
         <v>0</v>
@@ -31368,19 +31365,19 @@
         <v>741</v>
       </c>
       <c r="B703" t="n">
-        <v>996</v>
+        <v>963</v>
       </c>
       <c r="C703" t="n">
-        <v>0.103372440188289</v>
+        <v>0.0502277251458878</v>
       </c>
       <c r="D703" t="n">
         <v>0</v>
       </c>
       <c r="E703" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F703" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="G703" t="s">
         <v>20</v>
@@ -31389,16 +31386,16 @@
         <v>15</v>
       </c>
       <c r="I703" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J703" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K703" t="s">
         <v>15</v>
       </c>
       <c r="L703" t="n">
-        <v>10.34</v>
+        <v>5.02</v>
       </c>
       <c r="M703" t="n">
         <v>0</v>
@@ -31412,13 +31409,13 @@
         <v>996</v>
       </c>
       <c r="C704" t="n">
-        <v>0.0724475641259442</v>
+        <v>0.103372440188289</v>
       </c>
       <c r="D704" t="n">
         <v>0</v>
       </c>
       <c r="E704" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F704" t="s">
         <v>14</v>
@@ -31439,7 +31436,7 @@
         <v>15</v>
       </c>
       <c r="L704" t="n">
-        <v>7.24</v>
+        <v>10.34</v>
       </c>
       <c r="M704" t="n">
         <v>0</v>
@@ -31453,13 +31450,13 @@
         <v>996</v>
       </c>
       <c r="C705" t="n">
-        <v>0.0553445961393135</v>
+        <v>0.0724475641259442</v>
       </c>
       <c r="D705" t="n">
         <v>0</v>
       </c>
       <c r="E705" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F705" t="s">
         <v>14</v>
@@ -31480,7 +31477,7 @@
         <v>15</v>
       </c>
       <c r="L705" t="n">
-        <v>5.53</v>
+        <v>7.24</v>
       </c>
       <c r="M705" t="n">
         <v>0</v>
@@ -31494,13 +31491,13 @@
         <v>996</v>
       </c>
       <c r="C706" t="n">
-        <v>0.0751118828575155</v>
+        <v>0.0553445961393135</v>
       </c>
       <c r="D706" t="n">
         <v>0</v>
       </c>
       <c r="E706" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F706" t="s">
         <v>14</v>
@@ -31521,7 +31518,7 @@
         <v>15</v>
       </c>
       <c r="L706" t="n">
-        <v>7.51</v>
+        <v>5.53</v>
       </c>
       <c r="M706" t="n">
         <v>0</v>
@@ -31535,13 +31532,13 @@
         <v>996</v>
       </c>
       <c r="C707" t="n">
-        <v>0.0505889544380971</v>
+        <v>0.0751118828575155</v>
       </c>
       <c r="D707" t="n">
         <v>0</v>
       </c>
       <c r="E707" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F707" t="s">
         <v>14</v>
@@ -31562,7 +31559,7 @@
         <v>15</v>
       </c>
       <c r="L707" t="n">
-        <v>5.06</v>
+        <v>7.51</v>
       </c>
       <c r="M707" t="n">
         <v>0</v>
@@ -31576,7 +31573,7 @@
         <v>996</v>
       </c>
       <c r="C708" t="n">
-        <v>0.0504629749373369</v>
+        <v>0.0505889544380971</v>
       </c>
       <c r="D708" t="n">
         <v>0</v>
@@ -31603,9 +31600,50 @@
         <v>15</v>
       </c>
       <c r="L708" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="M708" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="s">
+        <v>747</v>
+      </c>
+      <c r="B709" t="n">
+        <v>996</v>
+      </c>
+      <c r="C709" t="n">
+        <v>0.0504629749373369</v>
+      </c>
+      <c r="D709" t="n">
+        <v>0</v>
+      </c>
+      <c r="E709" t="n">
+        <v>6</v>
+      </c>
+      <c r="F709" t="s">
+        <v>14</v>
+      </c>
+      <c r="G709" t="s">
+        <v>20</v>
+      </c>
+      <c r="H709" t="s">
+        <v>15</v>
+      </c>
+      <c r="I709" t="s">
+        <v>21</v>
+      </c>
+      <c r="J709" t="s">
+        <v>17</v>
+      </c>
+      <c r="K709" t="s">
+        <v>15</v>
+      </c>
+      <c r="L709" t="n">
         <v>5.05</v>
       </c>
-      <c r="M708" t="n">
+      <c r="M709" t="n">
         <v>0</v>
       </c>
     </row>
